--- a/output/Data and Chart Outputs/chile_power_by_type.xlsx
+++ b/output/Data and Chart Outputs/chile_power_by_type.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generation by type" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Generation by type" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -141,13 +141,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -157,6 +157,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -171,10 +172,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -199,10 +200,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -227,10 +228,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -255,10 +256,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -283,10 +284,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E87BA4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -311,10 +312,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="9A9A9A"/>
+            <a:solidFill>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -330,6 +331,34 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="9A9A9A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart'!$A$2:$A$65</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$H$2:$H$65</f>
+            </numRef>
+          </val>
+        </ser>
         <gapWidth val="30"/>
         <overlap val="100"/>
         <axId val="10"/>
@@ -341,11 +370,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -362,8 +403,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -373,13 +414,14 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -387,12 +429,13 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -401,10 +444,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -416,9 +459,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -750,6 +793,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -760,10 +804,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chile, monthly from 2021-01 to 2026-04. Ember lags real time by a few months; the weekly run picks up new months as they're released.</t>
-        </is>
-      </c>
-    </row>
+          <t>Monthly. Chile: 2021-01 to 2026-04. Ember lags real time by one to several months (it varies by country); the weekly run picks up new months as they're released.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -774,7 +819,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ember monthly electricity data (free, CC-BY-4.0): https://storage.googleapis.com/emb-prod-bkt-publicdata/public-downloads/monthly_full_release_long_format.csv. For Chile Ember's source is the Coordinador Electrico Nacional.</t>
+          <t>Ember monthly electricity data (free, CC-BY-4.0): https://storage.googleapis.com/emb-prod-bkt-publicdata/public-downloads/monthly_full_release_long_format.csv. Ember compiles each country's grid operator / ministry data (e.g. Chile: Coordinador Electrico Nacional; Brazil: ONS; Colombia: XM).</t>
         </is>
       </c>
     </row>
@@ -789,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -828,6 +873,11 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
@@ -852,6 +902,9 @@
         <v>2360</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>360</v>
       </c>
     </row>
@@ -875,6 +928,9 @@
         <v>2130</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>510</v>
       </c>
     </row>
@@ -898,6 +954,9 @@
         <v>2640</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>490</v>
       </c>
     </row>
@@ -921,6 +980,9 @@
         <v>2510</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>350</v>
       </c>
     </row>
@@ -944,6 +1006,9 @@
         <v>2670</v>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>370</v>
       </c>
     </row>
@@ -967,6 +1032,9 @@
         <v>2580</v>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>300</v>
       </c>
     </row>
@@ -990,6 +1058,9 @@
         <v>2830</v>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>630</v>
       </c>
     </row>
@@ -1013,6 +1084,9 @@
         <v>2260</v>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>640</v>
       </c>
     </row>
@@ -1036,6 +1110,9 @@
         <v>2060</v>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>270</v>
       </c>
     </row>
@@ -1059,6 +1136,9 @@
         <v>1890</v>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>290</v>
       </c>
     </row>
@@ -1082,6 +1162,9 @@
         <v>1780</v>
       </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>300</v>
       </c>
     </row>
@@ -1105,6 +1188,9 @@
         <v>1960</v>
       </c>
       <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
         <v>380</v>
       </c>
     </row>
@@ -1128,6 +1214,9 @@
         <v>1730</v>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
         <v>390</v>
       </c>
     </row>
@@ -1151,6 +1240,9 @@
         <v>1680</v>
       </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>360</v>
       </c>
     </row>
@@ -1174,6 +1266,9 @@
         <v>2160</v>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>350</v>
       </c>
     </row>
@@ -1197,6 +1292,9 @@
         <v>1890</v>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>540</v>
       </c>
     </row>
@@ -1220,6 +1318,9 @@
         <v>2140</v>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>450</v>
       </c>
     </row>
@@ -1243,6 +1344,9 @@
         <v>2020</v>
       </c>
       <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
         <v>530</v>
       </c>
     </row>
@@ -1266,6 +1370,9 @@
         <v>1990</v>
       </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
         <v>370</v>
       </c>
     </row>
@@ -1289,6 +1396,9 @@
         <v>1570</v>
       </c>
       <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>290</v>
       </c>
     </row>
@@ -1312,6 +1422,9 @@
         <v>1070</v>
       </c>
       <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
         <v>320</v>
       </c>
     </row>
@@ -1335,6 +1448,9 @@
         <v>920</v>
       </c>
       <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
         <v>260</v>
       </c>
     </row>
@@ -1358,6 +1474,9 @@
         <v>890</v>
       </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
         <v>290</v>
       </c>
     </row>
@@ -1381,6 +1500,9 @@
         <v>1100</v>
       </c>
       <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
         <v>320</v>
       </c>
     </row>
@@ -1404,6 +1526,9 @@
         <v>1070</v>
       </c>
       <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
         <v>330</v>
       </c>
     </row>
@@ -1427,6 +1552,9 @@
         <v>1080</v>
       </c>
       <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
         <v>330</v>
       </c>
     </row>
@@ -1450,6 +1578,9 @@
         <v>1350</v>
       </c>
       <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
         <v>350</v>
       </c>
     </row>
@@ -1473,6 +1604,9 @@
         <v>1440</v>
       </c>
       <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
         <v>340</v>
       </c>
     </row>
@@ -1496,6 +1630,9 @@
         <v>1540</v>
       </c>
       <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
         <v>370</v>
       </c>
     </row>
@@ -1519,6 +1656,9 @@
         <v>1300</v>
       </c>
       <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
         <v>310</v>
       </c>
     </row>
@@ -1542,6 +1682,9 @@
         <v>1140</v>
       </c>
       <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
         <v>290</v>
       </c>
     </row>
@@ -1565,6 +1708,9 @@
         <v>1190</v>
       </c>
       <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
         <v>280</v>
       </c>
     </row>
@@ -1588,6 +1734,9 @@
         <v>960</v>
       </c>
       <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
         <v>290</v>
       </c>
     </row>
@@ -1611,6 +1760,9 @@
         <v>980</v>
       </c>
       <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
         <v>260</v>
       </c>
     </row>
@@ -1634,6 +1786,9 @@
         <v>890</v>
       </c>
       <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
         <v>270</v>
       </c>
     </row>
@@ -1657,6 +1812,9 @@
         <v>1030</v>
       </c>
       <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
         <v>310</v>
       </c>
     </row>
@@ -1680,6 +1838,9 @@
         <v>960</v>
       </c>
       <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
         <v>290</v>
       </c>
     </row>
@@ -1703,6 +1864,9 @@
         <v>1220</v>
       </c>
       <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
         <v>340</v>
       </c>
     </row>
@@ -1726,6 +1890,9 @@
         <v>1280</v>
       </c>
       <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
         <v>310</v>
       </c>
     </row>
@@ -1749,6 +1916,9 @@
         <v>1540</v>
       </c>
       <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
         <v>320</v>
       </c>
     </row>
@@ -1772,6 +1942,9 @@
         <v>1500</v>
       </c>
       <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
         <v>320</v>
       </c>
     </row>
@@ -1795,6 +1968,9 @@
         <v>1030</v>
       </c>
       <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
         <v>250</v>
       </c>
     </row>
@@ -1818,6 +1994,9 @@
         <v>1010</v>
       </c>
       <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
         <v>280</v>
       </c>
     </row>
@@ -1841,6 +2020,9 @@
         <v>950</v>
       </c>
       <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
         <v>290</v>
       </c>
     </row>
@@ -1864,6 +2046,9 @@
         <v>930</v>
       </c>
       <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
         <v>290</v>
       </c>
     </row>
@@ -1887,6 +2072,9 @@
         <v>800</v>
       </c>
       <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
         <v>270</v>
       </c>
     </row>
@@ -1910,6 +2098,9 @@
         <v>850</v>
       </c>
       <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
         <v>220</v>
       </c>
     </row>
@@ -1933,6 +2124,9 @@
         <v>840</v>
       </c>
       <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
         <v>220</v>
       </c>
     </row>
@@ -1956,6 +2150,9 @@
         <v>790</v>
       </c>
       <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
         <v>260</v>
       </c>
     </row>
@@ -1979,6 +2176,9 @@
         <v>940</v>
       </c>
       <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
         <v>260</v>
       </c>
     </row>
@@ -2002,6 +2202,9 @@
         <v>1390</v>
       </c>
       <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
         <v>260</v>
       </c>
     </row>
@@ -2025,6 +2228,9 @@
         <v>1180</v>
       </c>
       <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
         <v>360</v>
       </c>
     </row>
@@ -2048,6 +2254,9 @@
         <v>1420</v>
       </c>
       <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
         <v>320</v>
       </c>
     </row>
@@ -2071,6 +2280,9 @@
         <v>1460</v>
       </c>
       <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
         <v>380</v>
       </c>
     </row>
@@ -2094,6 +2306,9 @@
         <v>1670</v>
       </c>
       <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
         <v>310</v>
       </c>
     </row>
@@ -2117,6 +2332,9 @@
         <v>1360</v>
       </c>
       <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
         <v>270</v>
       </c>
     </row>
@@ -2140,6 +2358,9 @@
         <v>1340</v>
       </c>
       <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
         <v>260</v>
       </c>
     </row>
@@ -2163,6 +2384,9 @@
         <v>1120</v>
       </c>
       <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
         <v>270</v>
       </c>
     </row>
@@ -2186,6 +2410,9 @@
         <v>1140</v>
       </c>
       <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2209,6 +2436,9 @@
         <v>1260</v>
       </c>
       <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2232,6 +2462,9 @@
         <v>920</v>
       </c>
       <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
         <v>260</v>
       </c>
     </row>
@@ -2255,6 +2488,9 @@
         <v>950</v>
       </c>
       <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
         <v>250</v>
       </c>
     </row>
@@ -2278,6 +2514,9 @@
         <v>1440</v>
       </c>
       <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
         <v>280</v>
       </c>
     </row>
@@ -2301,6 +2540,9 @@
         <v>1280</v>
       </c>
       <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
         <v>320</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/chile_power_by_type.xlsx
+++ b/output/Data and Chart Outputs/chile_power_by_type.xlsx
@@ -152,6 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Chile power generation by type (to Apr/26)</a:t>
             </a:r>
           </a:p>
@@ -804,7 +805,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Monthly. Chile: 2021-01 to 2026-04. Ember lags real time by one to several months (it varies by country); the weekly run picks up new months as they're released.</t>
+          <t>Monthly. Chile: 2021-01 to 2026-04. Ember lags real time by one to several months (it varies by country); each scheduled run picks up new months as they're released.</t>
         </is>
       </c>
     </row>
